--- a/src/out_season.xlsx
+++ b/src/out_season.xlsx
@@ -416,7 +416,7 @@
         <v>Generated</v>
       </c>
       <c r="B2" t="str">
-        <v>8/21/2026, 1:45:54 PM</v>
+        <v>8/21/2026, 1:59:31 PM</v>
       </c>
     </row>
     <row r="3">

--- a/src/out_season.xlsx
+++ b/src/out_season.xlsx
@@ -416,7 +416,7 @@
         <v>Generated</v>
       </c>
       <c r="B2" t="str">
-        <v>8/21/2026, 1:59:31 PM</v>
+        <v>8/24/2026, 3:19:14 PM</v>
       </c>
     </row>
     <row r="3">
@@ -424,7 +424,7 @@
         <v>Games</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -432,7 +432,7 @@
         <v>Record</v>
       </c>
       <c r="B4" t="str">
-        <v>3-2-0</v>
+        <v>1-2-0</v>
       </c>
     </row>
     <row r="5">
@@ -440,7 +440,7 @@
         <v>Goals for</v>
       </c>
       <c r="B5">
-        <v>123</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -448,7 +448,7 @@
         <v>Goals against</v>
       </c>
       <c r="B6">
-        <v>87</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -456,7 +456,7 @@
         <v>Goal differential</v>
       </c>
       <c r="B7">
-        <v>36</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="8">
@@ -464,7 +464,7 @@
         <v>Goals for / game</v>
       </c>
       <c r="B8">
-        <v>24.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -472,7 +472,7 @@
         <v>Goals against / game</v>
       </c>
       <c r="B9">
-        <v>17.4</v>
+        <v>7.67</v>
       </c>
     </row>
   </sheetData>
@@ -484,7 +484,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:T9"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -505,6 +505,7 @@
     <col min="17" max="17" width="10.83203125" customWidth="1"/>
     <col min="18" max="18" width="10.83203125" customWidth="1"/>
     <col min="19" max="19" width="10.83203125" customWidth="1"/>
+    <col min="20" max="20" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -518,51 +519,54 @@
         <v>GP</v>
       </c>
       <c r="D1" t="str">
+        <v>Minutes</v>
+      </c>
+      <c r="E1" t="str">
         <v>Goals</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Shots</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Shot %</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Goals per Game</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Assists</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>Steals</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>Blocks</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>Turnovers</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>7's Drawn</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>7's Made</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>7's Missed</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>2 Min</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>2's Drawn</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>Yellow</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>Red</v>
       </c>
-      <c r="S1" t="str">
+      <c r="T1" t="str">
         <v>Points</v>
       </c>
     </row>
@@ -574,40 +578,40 @@
         <v>Jack</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>57.1</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>8.8</v>
+        <v>65</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>4.33</v>
       </c>
       <c r="I2">
         <v>3</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -622,154 +626,163 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>51</v>
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B3" t="str">
-        <v>Ryan</v>
+        <v>RJ</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>78.1</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>44.4</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B4" t="str">
-        <v>RJ</v>
+        <v>Ryan</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>60.6</v>
+        <v>2</v>
       </c>
       <c r="G4">
+        <v>50</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
         <v>4</v>
-      </c>
-      <c r="H4">
-        <v>9</v>
-      </c>
-      <c r="I4">
-        <v>4</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>7</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>5</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v/>
       </c>
       <c r="B5" t="str">
         <v>Charlie</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>57.1</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -799,45 +812,48 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
+      <c r="A6">
+        <v>18</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Evan</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="str">
         <v/>
       </c>
-      <c r="B6" t="str">
-        <v>Roman</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>15</v>
-      </c>
-      <c r="F6">
-        <v>46.7</v>
-      </c>
-      <c r="G6">
-        <v>1.75</v>
-      </c>
       <c r="H6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -858,42 +874,45 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>11</v>
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B7" t="str">
-        <v>Evan</v>
+        <v>Barrett</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>50</v>
-      </c>
-      <c r="G7">
-        <v>1.25</v>
+        <v>0</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -905,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="O7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -917,42 +936,45 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B8" t="str">
-        <v>Barrett</v>
+        <v>Sean</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>50</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G8" t="str">
+        <v/>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -964,7 +986,7 @@
         <v>0</v>
       </c>
       <c r="O8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -976,36 +998,39 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Ben</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" t="str">
         <v/>
       </c>
-      <c r="B9" t="str">
-        <v>Sean</v>
-      </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-      <c r="D9">
-        <v>4</v>
-      </c>
-      <c r="E9">
-        <v>5</v>
-      </c>
-      <c r="F9">
-        <v>80</v>
-      </c>
-      <c r="G9">
-        <v>1.33</v>
-      </c>
       <c r="H9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1026,7 +1051,7 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1035,137 +1060,22 @@
         <v>0</v>
       </c>
       <c r="S9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v/>
-      </c>
-      <c r="B10" t="str">
-        <v>Christian</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10">
-        <v>3</v>
-      </c>
-      <c r="E10">
-        <v>5</v>
-      </c>
-      <c r="F10">
-        <v>60</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v/>
-      </c>
-      <c r="B11" t="str">
-        <v>Ben</v>
-      </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
-      <c r="F11">
-        <v>100</v>
-      </c>
-      <c r="G11">
-        <v>0.67</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>1</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>1</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:K2"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -1177,6 +1087,7 @@
     <col min="8" max="8" width="12.83203125" customWidth="1"/>
     <col min="9" max="9" width="12.83203125" customWidth="1"/>
     <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1210,6 +1121,9 @@
       <c r="J1" t="str">
         <v>Saves After Whistle</v>
       </c>
+      <c r="K1" t="str">
+        <v>Empty Net Goals</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -1219,72 +1133,43 @@
         <v>Corn</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>135</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>43</v>
+        <v>42.1</v>
       </c>
       <c r="G2">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="H2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v/>
-      </c>
-      <c r="B3" t="str">
-        <v>Crane</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>19</v>
-      </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>47.4</v>
-      </c>
-      <c r="G3">
-        <v>10</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J4"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -1347,19 +1232,19 @@
         <v>L (est.)</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="H2">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="I2" t="str">
-        <v>Jack (10)</v>
+        <v>Jack (6)</v>
       </c>
       <c r="J2" t="str">
-        <v>2025_Season_Legacy.xlsx (legacy sheet)</v>
+        <v>legacy_fixture.xlsx (legacy sheet)</v>
       </c>
     </row>
     <row r="3">
@@ -1367,7 +1252,7 @@
         <v/>
       </c>
       <c r="B3" t="str">
-        <v>West Point UNC</v>
+        <v>SUNY</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -1376,123 +1261,59 @@
         <v/>
       </c>
       <c r="E3" t="str">
-        <v>W (est.)</v>
+        <v>L (est.)</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H3">
-        <v>21</v>
+        <v>-3</v>
       </c>
       <c r="I3" t="str">
-        <v>Jack (12)</v>
+        <v>Jack (5)</v>
       </c>
       <c r="J3" t="str">
-        <v>2025_Season_Legacy.xlsx (legacy sheet)</v>
+        <v>legacy_fixture.xlsx (legacy sheet)</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v/>
+        <v>2026-08-24</v>
       </c>
       <c r="B4" t="str">
-        <v>SUNY</v>
+        <v>Army</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v>Home</v>
       </c>
       <c r="D4" t="str">
-        <v/>
+        <v>Regular season</v>
       </c>
       <c r="E4" t="str">
-        <v>W (est.)</v>
+        <v>W</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G4">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I4" t="str">
-        <v>RJ (8)</v>
+        <v>Jack (2)</v>
       </c>
       <c r="J4" t="str">
-        <v>2025_Season_Legacy.xlsx (legacy sheet)</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v/>
-      </c>
-      <c r="B5" t="str">
-        <v>Treasuer Cove</v>
-      </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v>L (est.)</v>
-      </c>
-      <c r="F5">
-        <v>30</v>
-      </c>
-      <c r="G5">
-        <v>31</v>
-      </c>
-      <c r="H5">
-        <v>-1</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Jack (14)</v>
-      </c>
-      <c r="J5" t="str">
-        <v>2025_Season_Legacy.xlsx (legacy sheet)</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>2026-08-21</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Army</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Home</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Regular season</v>
-      </c>
-      <c r="E6" t="str">
-        <v>W</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Jack (2)</v>
-      </c>
-      <c r="J6" t="str">
         <v>this browser</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
   </ignoredErrors>
 </worksheet>
 </file>